--- a/Entry_and_Exist_report/output/Daily_Breakdown_Report.xlsx
+++ b/Entry_and_Exist_report/output/Daily_Breakdown_Report.xlsx
@@ -8,7 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="24 August " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="21 August " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="26 August " sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="25 August " sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="24 August " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="23 August " sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -521,7 +525,7 @@
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -530,10 +534,10 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>0</v>
@@ -568,10 +572,10 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0</v>
@@ -587,10 +591,10 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>0</v>
@@ -606,27 +610,4357 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>FROM 5 AM TO 6 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>FROM 6 AM TO 7 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>FROM 7 AM TO 8 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>FROM 8 AM TO 9 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>FROM 9 AM TO 10 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>FROM 5 AM TO 6 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>FROM 6 AM TO 7 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>FROM 7 AM TO 8 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>FROM 8 AM TO 9 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>FROM 9 AM TO 10 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>FROM 5 AM TO 6 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>FROM 6 AM TO 7 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>FROM 7 AM TO 8 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>FROM 8 AM TO 9 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>FROM 9 AM TO 10 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>FROM 5 AM TO 6 AM</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>FROM 6 AM TO 7 AM</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>FROM 7 AM TO 8 AM</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>FROM 8 AM TO 9 AM</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>FROM 9 AM TO 10 AM</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A12:A16"/>
     <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date of B/D</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Time of B/D</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Driver Emp No #</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asset Number </t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Bus No.</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Type Of B/D</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Operation Action</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re-Operations time </t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>W/S Comments</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reported Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1ST BATCH - FROM 5 AM TO 6 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.2458333333333333</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2184268</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PTS1409</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>92/9540</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Front   Right  Side  Socket  Ambrose  Road  Broken  Check &amp;   Replace </t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2025-08-21 06:37</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.2152777777777778</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174279 </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PTS1297</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>92/6906</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> A/C  Not  Working  &amp; Over  Heat </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2025-08-21 06:39</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.2152777777777778</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2244077</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PTS1389</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>92/9518</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Starting  Defect  &amp;  Check &amp; Replace  Battery   New    &amp;  On  Running  Time  Engine   Off </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2025-08-21 06:39</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2194093</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PTS1241</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>92/6918</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Steering   Wheel    Hard &amp;  Jam Tide Check   Oil  </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2025-08-21 06:35</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2ND BATCH - FROM 6 AM TO 7 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.2638888888888889</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2189056</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PTS1332</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>92/6885</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Murughab</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Front   Door   Switch   Defect  </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2025-08-21 10:06</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>3RD BATCH - FROM 7 AM TO 8 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2144096</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PTS1543</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>92/9512</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Murughab</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Air   Leaks  &amp;  Radiator  Need   To  washing  Cling  </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:45</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2234048</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PTS1265</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>92/6893</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Murughab</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Rear LHS balloon </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.3152777777777778</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2244054</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PTS1271</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>92/6910</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OVER HEAT AIR LEAK</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:43</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0.3229166666666667</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174235 </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PTS1493</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>92/9452</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts </t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRONT DOOR DEFAECT  </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2025-08-21 10:13</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0.3194444444444444</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184020 </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PTS1557</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>92/9545</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb  to pts  </t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mirror frame RHS DEFECT  </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2025-08-21 10:15</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>4TH BATCH - FROM 8 AM TO 9 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234048 </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PTS1265</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>92/6893</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts  </t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake  Adjusting   &amp;   Right Side Front   Wheel   Sound   Coming  &amp; Socket  Ambrose  Check </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0.3368055555555556</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2194125 </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PTS1393</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>92/9421</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kahiatn To pts  </t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Front   Balloon  Air   Leaks  &amp; Steering  Wheel    wobbling   Too  Much </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2025-08-21 10:20</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0.3506944444444444</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234118 </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PTS1459</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>92/9497</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts  </t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Over   Heat   &amp;  Air  Leaks  &amp;  All  Lighting  Systems   Check &amp;  Repairs </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2025-08-21 10:20</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0.3472222222222222</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2184477</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PTS1359</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>92/9010</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shariq  To  pts  </t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Air   Leaks  &amp;  Radiator  Need   To  washing  Cling  </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2025-08-21 10:21</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8:52</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234081 </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PTS1435</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>92/9487</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maliya </t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Rear LHS balloon </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2025-08-21 13:58</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>5TH BATCH - FROM 9 AM TO 10 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 9:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174225 </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PTS1338</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>92/6968</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OVER HEAT AIR LEAK</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2025-08-21 13:58</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 9:04</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2189085 </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PTS1248</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>92/7013</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRONT DOOR DEFAECT  </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2025-08-21 13:59</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 9:36</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174231 </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PTS1249</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>92/6944</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MALIAY </t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mirror frame RHS DEFECT  </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2244021 </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PTS1538</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>92/9447</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JleEB To Pts  </t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake  Adjusting   &amp;   Right Side Front   Wheel   Sound   Coming  &amp; Socket  Ambrose  Check </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2144340 </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PTS1367</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>92/9018</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb To Pts  </t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Front   Balloon  Air   Leaks  &amp; Steering  Wheel    wobbling   Too  Much </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0.4131944444444444</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234120 </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PTS1324</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>92/6933</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Jleeb to pts </t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Over   Heat   &amp;  Air  Leaks  &amp;  All  Lighting  Systems   Check &amp;  Repairs </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A21:L21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date of B/D</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Time of B/D</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Driver Emp No #</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asset Number </t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Bus No.</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Type Of B/D</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Operation Action</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re-Operations time </t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>W/S Comments</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reported Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1ST BATCH - FROM 5 AM TO 6 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2174206</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PTS1287</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>92/7003</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>A/C Belt Broken</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2025-08-26 06:21</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>92/6953</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PTS1321</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>92/6953</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Rear Right Side Both Tires Burst</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:22</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>92/6939</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PTS1252</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>92/6939</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Oil pressure sensor defect</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.2423611111111111</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2134366</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PTS1585</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>92/9411</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Air leak , cabin  door  defect</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2025-08-26 13:29</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2244078</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PTS1447</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>92/9557</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear Right side outer tire puncher </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:22</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2ND BATCH - FROM 6 AM TO 7 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.2701388888888889</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2184557</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PTS1260</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>92/6946</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HASAWI </t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air leak </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:22</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2234004</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PTS1421</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>92/9435</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliay  </t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poor brake ,  steering play ,  vibration </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:21</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>3RD BATCH - FROM 7 AM TO 8 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.2930555555555556</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2174307</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PTS1495</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>92/9419</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Poor  pick  up , A/c defect</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:18</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0.2965277777777778</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2244033</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PTS1373</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>92/9024</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Front   door defect , Rear Right side tire need Replacement </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:20</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0.2965277777777778</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2184157</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PTS1263</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>92/6887</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Air  leak </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:20</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.3173611111111111</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2184540</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PTS1354</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>92/9005</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Mirqab</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air leak </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:10</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2174033</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PTS1506</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>92/9578</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salmiya </t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear left side outer tire puncher </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:23</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2184116</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PTS1436</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>92/9469</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>mirqab</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gear slipping </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:25</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>4TH BATCH - FROM 8 AM TO 9 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2104071 </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PTS1374</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>92/9025</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shaban To pts  </t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Left Side Rear   Inner  Tire   Puncher </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:10</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0.3402777777777778</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2224033 </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PTS1476</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>92/9532</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb to pts </t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake  Adjusting &amp; Balloon  Defect Sound Coming </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:11</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0.3645833333333333</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2162333</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PTS1490</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>92/9474</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts  </t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Right  Rear  Outer  Tire  Blast  </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:09</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174258 </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PTS1358</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>92/9009</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salmiya  to pts  </t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Right  Side  Rear  Inner  Tire  Blast </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:11</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>5TH BATCH - FROM 9 AM TO 10 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0.3993055555555556</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2194129</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MOE353</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>92/8951</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shuwaikh  to g1 </t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Front   Door   air  Leaks </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:29</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.3993055555555556</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234087 </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PTS1244</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>92/6891</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts  </t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> All  Tire   Air  Check &amp;  Horan  Not  Working  </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:29</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2064054 </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PTS1243</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>92/6912</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Riggae To pts </t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Over  Heat  &amp;    Water   Leaks &amp; Brake &amp;  Hand   Brake   Defect  </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:30</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>6TH BATCH - FROM 9 AM TO 10 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>18</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.3993055555555556</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2194129</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MOE353</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>92/8951</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shuwaikh  to g1 </t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Front   Door   air  Leaks </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:29</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>19</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0.3993055555555556</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234087 </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PTS1244</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>92/6891</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts  </t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> All  Tire   Air  Check &amp;  Horan  Not  Working  </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:29</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>20</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2064054 </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PTS1243</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>92/6912</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Riggae To pts </t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Over  Heat  &amp;    Water   Leaks &amp; Brake &amp;  Hand   Brake   Defect  </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:30</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A27:L27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date of B/D</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Time of B/D</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Driver Emp No #</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asset Number </t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Bus No.</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Type Of B/D</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Operation Action</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re-Operations time </t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>W/S Comments</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reported Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1ST BATCH - FROM 5 AM TO 6 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.2340277777777778</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2064054</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PTS1422</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>92/9574</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Reggai</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>A/c pulley    sound</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2ND BATCH - FROM 6 AM TO 7 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2053309</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PTS1340</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>92/6874</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Farwaniya </t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Break Defect &amp; Front Door Air Leak </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2025-08-25 08:34</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.2743055555555556</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2244069 </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PTS1237</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>92/6924</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kaithan </t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Over Heat &amp; A/C Cut Off </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2025-08-25 09:06</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.2784722222222222</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2134479</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PTS1361</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>92/9012</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear Right side inner tire puncher </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2025-08-25 08:33</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2234100</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PTS1416</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>92/9501</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliya </t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuse box door lock defect  </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2025-08-25 08:33</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.2861111111111111</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2234068</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PTS1280</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>92/6890</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliya </t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear Right side  Outer   tire  puncher </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2025-08-25 09:06</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>3RD BATCH - FROM 7 AM TO 8 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.2951388888888889</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2174529</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MOE331</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>92/8929</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear Right side outer tire blast ,  poor pick up </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:55</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.3020833333333333</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2184137</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PTS1293</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>92/6988</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salmiya </t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Front Side Stearing Wobbling &amp; All Balloon Check  </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2025-08-25 08:33</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2164040</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PTS1514</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>92/9495</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hasawi </t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Over Heat &amp; Left Side Break Alarm &amp; Air Leak  </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2025-08-25 09:07</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2234048</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PTS1457</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>92/9480</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hasawi </t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air Leak &amp; Rear Right Side Break Jam </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2025-08-25 06:07</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.3229166666666667</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174364 </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PTS1214</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>92/6901</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliya </t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Break Jam &amp; Break Defect </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2025-08-25 09:42</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.3229166666666667</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2224020</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PTS1554</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>92/9486</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliya </t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air leak , Over  heat </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2025-08-25 09:37</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0.3277777777777778</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2184132</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PTS1265</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>92/6893</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sharq</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Over heat </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2025-08-25 09:47</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>4TH BATCH - FROM 8 AM TO 9 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0.3472222222222222</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2184361</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PTS1612</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Zhong tong</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Murgab to pts</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right Side Rear  wheel   Brake  Jam &amp;  Smoke  Coming </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2025-08-25 10:32</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8:40</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PTS1522</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PTS1522</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>92/9543</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MURGAB  </t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear door defect Engine oil top up brake adjust  parking light defect  </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2025-08-25 10:33</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0.3472222222222222</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234091 </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PTS1504</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>92/9499</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb  to pts </t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Left  Side front  wheel  brake Jam &amp; Sound Coming &amp;  Rear  Both Of  side  Wheel  Brake  Defect  &amp; Check Brake Liner Replace </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:54</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0.3506944444444444</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184540 </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PTS1354</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>92/9005</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murgab to pts  </t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Air   Leaks    &amp;   Bubbling   too  Much </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2025-08-25 10:34</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0.3486111111111111</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2174046</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PTS1579</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>92/9555</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salmiya To pts </t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Air   Leaks  &amp;  Air Compressors  Check </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2025-08-25 13:50</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>5TH BATCH - FROM 9 AM TO 10 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.3784722222222222</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184046 </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PTS1578</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>92/9554</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb To pts </t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Red Yellow  Indication &amp; On  Running Time   Engine   Off  &amp;   Low  Pick up </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2025-08-25 10:33</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174231 </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PTS1249</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>92/6944</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts </t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Horan &amp;  Right   Side Rear  Inner  Tire  Puncher </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:54</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234095 </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PTS1262</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>92/6983</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murgab to pts  </t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Right  Side  Rear  Inner  Tire   Puncher </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:55</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.3854166666666667</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174529 </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MOE331</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>92/8929</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jahra To pts </t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Clutch  &amp; Low Pick up &amp; Hand  Brake </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:55</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0.4027777777777778</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2134474 </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PTS1233</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>92/6928</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts </t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake  &amp;  Hand  Brake defect &amp; rear Both Of side  4  Th  Tire   Replace  New Tire </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:55</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>0.3993055555555556</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2184152</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>MOE281</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>92/8878</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Salmiya  To pts</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Right  Side  Front   wheel  Brake  Jam &amp;  Front   Both Of Side Tire  Replace New </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2025-08-25 12:01</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>25</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2244002 </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PTS1356</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>92/9007</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb To pts  </t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> A/C  Blower Not  Working &amp;  Horan &amp;  Brake   Adjusting   </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:57</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>26</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 9:21</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184160 </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PTS1426</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>92/9581</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Farwaniya </t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> water leak &amp; over heat</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:57</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A4:L4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -760,7 +5094,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1013,7 +5347,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2329,7 +6663,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2482,7 +6816,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2844,7 +7178,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2997,7 +7331,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3011,4 +7345,1444 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date of B/D</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Time of B/D</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Driver Emp No #</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asset Number </t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Bus No.</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Type Of B/D</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Operation Action</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re-Operations time </t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>W/S Comments</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reported Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1ST BATCH - FROM 6 AM TO 7 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2234067</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PTS1292</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>92/6963</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PTS G1 </t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Back Right Side  Balloon Defect &amp; Air Leak &amp; Break Adjust</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2025-08-23 08:43</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234068 </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PTS1310</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>92/6978</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air Leak &amp; Oil Top Up </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:25</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174566 </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PTS1581</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>92/9576</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PTS G1 </t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Rear Right Side Outer Tire Puncher   &amp; Left Side Balloon Defect  &amp; Back Side Fan Belt Broken</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:25</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.2847222222222222</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2184292</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PTS1517</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>92/9542</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PTS G1 </t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air Leak </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:54</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2ND BATCH - FROM 7 AM TO 8 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2224062 </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PTS1573</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>92/9455</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sharg </t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air Leak </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2025-08-23 08:44</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184138 </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MOE280</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>92/8877</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb </t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A/C Defect &amp; Head Light Not Working </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2025-08-23 08:44</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.3020833333333333</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2154067 </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PTS1399</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>92/9528</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rigai </t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Left Side Balloon Defect </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:56</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.3090277777777778</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2224063</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PTS1217</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>92/6878</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sharg </t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red Indication Poor Pick Up </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:56</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2224052 </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PTS1309</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>92/6873</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air Leak &amp; Front Right Side Shockabserber Broken  </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:53</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0.3159722222222222</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2184116</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PTS1436</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>92/9469</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murughab </t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Break Jam </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Road Side Assistant</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2025-08-23 08:44</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2164052</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MOE359</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>92/8957</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Salmiya</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Rear Left Side Outer Tire Puncher</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2025-08-23 11:11</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.3194444444444444</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2134405</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PTS1365</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>92/9016</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Salmiya</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Front   Wheel   Wobbling   &amp;  Over  Heat </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2025-08-23 10:13</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.3229166666666667</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174364 </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PTS1214</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>92/6901</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake   Defect   Front   Wheel   Brake  Jam </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2025-08-23 14:13</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174315 </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PTS1252</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>92/6939</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murughab </t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake   Jam  &amp;  All    Lighting   Systems  </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2025-08-23 10:13</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174115 </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PTS1403</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>92/9442</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fahaheel  to pts </t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Left  Side Rear  Outer  Tire &amp; Right  Side Rear Inner  Tire  Puncher  &amp; Check &amp; Replace  &amp; Over   Heat  Coolant  &amp; All   Lighting   Systems   Check &amp;   Repairs </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2025-08-23 10:45</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>3RD BATCH - FROM 8 AM TO 9 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0.3368055555555556</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2115465</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MOE360</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>92/8958</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Shuwaikh</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right  Side   Rear   Outer   Tire Blast  </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:16</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0.3472222222222222</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184113 </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PTS1284</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>92/6964</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Right   Side  Rear   wheel Hub  Seal Oil Leaks  </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0.3541666666666667</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234118 </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PTS1459</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>92/9497</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Right   Side  Rear   Outer  Tire  Blast  Replace </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2025-08-23 10:45</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0.3645833333333333</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174177 </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PTS1363</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>92/9014</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Over  Heat  &amp;  Rear  wheel  Both Of Side  Brake   Defect &amp;  wiper   Check &amp; Replace </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2025-08-23 10:45</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0.3645833333333333</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2234122</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PTS1250</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>92/6941</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murughab </t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Wobbling   Too  Much  &amp; Coolant  Water </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:34</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2224071 </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PTS1393</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>92/9421</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Salmiya</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Steering   wheel  Hard  Tide &amp; wobbling </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2025-08-23 11:11</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>4TH BATCH - FROM 9 AM TO 10 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2234070</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PTS1253</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>92/6942</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Steering   wobbling   Too  Much &amp;  Brake  Defect  Rear  Both of wheel  &amp; Sound Coming  </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2025-08-23 10:46</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.3784722222222222</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184085 </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PTS1364</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>92/9015</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Break   Jam  &amp;   Smoke    Coming </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2025-08-23 11:23</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0.3819444444444444</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184028 </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PTS1296</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>92/6907</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Air   Leaks   &amp;  Brake  Defect </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2025-08-23 12:49</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2084015 </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PTS1258</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>92/6945</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Salmiya</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Front   Both  Of   Side  Balloon  &amp; Brake   Sound  Coming &amp;  All  Lighting  Systems  Check &amp;  Repairs </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2025-08-23 13:28</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0.4027777777777778</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2184445</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MOE375</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>92/8973</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Salmiya</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air   Leaks  &amp;  Brake  Jam &amp; Check &amp; Replace  Brake  Liner </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2025-08-23 11:12</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A7:L7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>